--- a/000 預測隔天.xlsx
+++ b/000 預測隔天.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\Taifex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2952A852-765A-4E43-964D-D933DFAACBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C495ED-093F-4C86-81B2-BFBBAD369BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C67879A0-8A12-4C2A-9592-0DBEE8CCF9FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C67879A0-8A12-4C2A-9592-0DBEE8CCF9FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Gemini 產生原資料命令" sheetId="2" r:id="rId1"/>
-    <sheet name="3家 數據都不同" sheetId="6" r:id="rId2"/>
-    <sheet name="工作表1 (2)" sheetId="7" r:id="rId3"/>
+    <sheet name="20因子" sheetId="7" r:id="rId2"/>
+    <sheet name="3家 數據都不同" sheetId="6" r:id="rId3"/>
     <sheet name="Ubuntu" sheetId="8" r:id="rId4"/>
+    <sheet name="LINE通知" sheetId="9" r:id="rId5"/>
+    <sheet name="程式" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="196">
   <si>
     <t>給我 2025/11/11 三大法人在交易口數與契約金額以及未平倉口數與契約金額上的多方、空方和多空淨額數據</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -713,102 +715,727 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01.20 06:50</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F16: 打開 網址 https://www.twse.com.tw/zh/trading/historical/stock-day.html     2330 台積電-當日(1000股=1張)  [請填入:成交張數]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F12: 打開 網址 https://www.twse.com.tw/zh/trading/historical/mi-index.html      大盤統計資訊  [請填入:總計成交金額]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F07: 打開 網址 https://www.taifex.com.tw/cht/3/pcRatio                臺指選擇權Put/Call比  [請填入:買賣權未平倉量比率%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F06: 打開 網址 https://mis.taifex.com.tw/futures/VolatilityQuotes     臺指選擇權波動率指數   [請填入:波動率指數]            </t>
+  </si>
+  <si>
+    <t>一般交易時段</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 查當日資料 當日無資料 轉查前一個交易日資料</t>
+  </si>
+  <si>
+    <t>💡 一個讓 Ubuntu 使用更順暢的小建議</t>
+  </si>
+  <si>
+    <t>如果你之後發現 claude 還是常噴權限錯誤，最好的長期解法是把全域 npm 的目錄改到你的家目錄下，這樣以後裝任何工具都不需要 sudo：</t>
+  </si>
+  <si>
+    <t>Bash</t>
+  </si>
+  <si>
+    <t># 建立一個給全域使用的目錄</t>
+  </si>
+  <si>
+    <t>mkdir ~/.npm-global</t>
+  </si>
+  <si>
+    <t># 設定 npm 使用新路徑</t>
+  </si>
+  <si>
+    <t>npm config set prefix '~/.npm-global'</t>
+  </si>
+  <si>
+    <t># 把路徑加入你的 .bashrc</t>
+  </si>
+  <si>
+    <t>echo 'export PATH=~/.npm-global/bin:$PATH' &gt;&gt; ~/.bashrc</t>
+  </si>
+  <si>
+    <t>source ~/.bashrc</t>
+  </si>
+  <si>
+    <t># 之後安裝就不用 sudo 了：npm install -g @anthropic-ai/claude-code</t>
+  </si>
+  <si>
+    <t>現在請試著執行 claude，看看能不能順利看到對話視窗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F01: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   臺股期貨-外資 多空淨額口數  [請填入:未平倉口數] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F02: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   臺股期貨-外資 多方口數      [請填入:未平倉口數] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F03: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   臺股期貨-外資 空方口數      [請填入:未平倉口數] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F04: 打開 網址 https://www.taifex.com.tw/cht/3/futDailyMarketReport   臺股期貨-當日收盤價    [請填入:最後成交價] [請填入:漲跌價差]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F05: 打開 網址 https://www.taifex.com.tw/cht/3/optDailyMarketReport   臺股期貨-當日選擇權    [請填入:選擇權總成交量] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F11: 打開 網址 https://www.twse.com.tw/zh/indices/taiex/mi-5min-hist.html       加權股價     [請填入:指數收盤] [請填入:漲跌價差]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F13: 打開 網址 https://www.wantgoo.com/index/0000                                                                   台灣加權股價指數與 20 日  [均線距離 ]              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F14: 打開 網址 https://www.twse.com.tw/zh/trading/historical/stock-day.html     2330 台積電-當日    [請填入:收盤價] [請填入:漲跌價差]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F17: 打開 網址 https://www.twse.com.tw/fund/BFI82U                              台灣股票外資及陸資 淨買賣額   [請填入:買賣差額]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          - F18 台灣股票外資及陸資 多方買額  [請填入:買額]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          - F19 台灣股票外資及陸資 空方賣額  [請填入:賣額]</t>
+  </si>
+  <si>
+    <t>------------------</t>
+  </si>
+  <si>
+    <t>盤後交易時段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F21: 打開 網址 [https://www.wantgoo.com/global]         NASDAQ指數    : 23,307.62   [漲跌 +301.26   +1.31%]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F22: 打開 網址 [https://www.wantgoo.com/global]         費城半導體指數  : 7,067.90 [漲跌 +204.30, +2.98%] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F23: 打開 網址 [https://www.wantgoo.com/global]         EM-ND期指數    : 25,135.75  [漲跌 +107.50, +0.43%] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F24: 打開 網址 [https://www.wantgoo.com/global]         台積電ADR      : 288.87       [漲跌 +4.19, +1.47%]         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            F25: 打開 網址 [https://www.wantgoo.com/global]         台指期盤後     : [請填入:最新價] [請填入:漲跌 , 漲幅] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     暫時不處理         F06: 打開 網址 https://mis.taifex.com.tw/futures/VolatilityQuotes     臺指選擇權波動率指數   [請填入:波動率指數]      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2026.01.29</t>
+  </si>
+  <si>
+    <t>📊 抓取結果摘要:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F01 臺股期貨-外資 多空淨額口數  [未平倉口數: -348563]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F02 臺股期貨-外資 多方口數  [未平倉口數: 237513]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F03 臺股期貨-外資 空方口數  [未平倉口數: 586076]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F04 臺股期貨-當日收盤價  [最後成交價: 32777]  [漲跌價差: -148]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F05 臺股期貨-當日選擇權  [選擇權總成交量: 245584]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F07 臺指選擇權Put/Call比  [買賣權未平倉量比率%: 134.57]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F11 加權股價  [指數收盤: 32536.27]  [漲跌價差: -267.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F12 大盤總交易額  [總計成交金額: 9596.52億]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F14 2330 台積電-當日  [收盤價: 1805.00]  [漲跌價差: -15.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F16 2330 台積電-當日(1000股=1張)  [成交張數: 36079張]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F17 台灣股票外資及陸資 淨買賣額  [買賣差額: +146.59億]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F18 台灣股票外資及陸資 多方買額  [買額: 3281.86億]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - F19 台灣股票外資及陸資 空方賣額  [賣額: 3135.27億]</t>
+  </si>
+  <si>
+    <t>如果你之後想更進一步，例如：</t>
+  </si>
+  <si>
+    <t>將抓到的數據自動畫成 K線圖或折線圖。</t>
+  </si>
+  <si>
+    <t>設定 LINE Notify 每天下午三點自動把報告發到手機。</t>
+  </si>
+  <si>
+    <t>增加 夜盤 (Nighttime) 的數據監控。</t>
+  </si>
+  <si>
+    <t>隨時跟我說，我們再繼續擴充這個專案！做得好！</t>
+  </si>
+  <si>
+    <t>這是一個非常實用的功能，能讓你即使不在電腦前，也能在第一時間透過手機收到當日的台指籌碼報告。這就像是為你的 N100 爬蟲裝上「推播通知」。</t>
+  </si>
+  <si>
+    <t>以下是這個功能的運作原理與設定步驟說明：</t>
+  </si>
+  <si>
+    <t>1. 運作原理</t>
+  </si>
+  <si>
+    <t>這項功能主要分為三個部分：</t>
+  </si>
+  <si>
+    <t>LINE Notify 服務：這是 LINE 提供的一個免費「通知管道」。它不具備聊天機器人的複雜對話功能，但非常適合用來發送單向的通知訊息（包含文字與圖片）。</t>
+  </si>
+  <si>
+    <t>Python 串接腳本：在你的 daytime_query.py 成功抓取並生成 .md 報告後，我們會加入一段程式碼，讀取報告內容並透過 HTTP 協定將資料傳送給 LINE。</t>
+  </si>
+  <si>
+    <t>定時執行：利用我們之前提到的排程工具，確保每天下午 3:00 自動觸發這套流程。</t>
+  </si>
+  <si>
+    <t>2. 設定步驟 (三個階段)</t>
+  </si>
+  <si>
+    <t>第一階段：取得 LINE 權杖 (Token)</t>
+  </si>
+  <si>
+    <t>前往 LINE Notify 官網 並登入你的帳號。</t>
+  </si>
+  <si>
+    <t>進入「個人頁面」，點選**「發行權杖」 (Generate token)**。</t>
+  </si>
+  <si>
+    <t>設定權杖名稱（例如：「台指籌碼助手」），並選擇要接收通知的聊天室（可以是自己，或一個專門放報告的群組）。</t>
+  </si>
+  <si>
+    <t>複製並保存這組 Token（它只會出現這一次）。</t>
+  </si>
+  <si>
+    <t>第二階段：在 Python 中加入發送代碼</t>
+  </si>
+  <si>
+    <t>我們只需要在原本的腳本末端加入類似以下的邏輯：</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>import requests</t>
+  </si>
+  <si>
+    <t>def send_line_notify(message, token):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    url = "https://notify-api.line.me/api/notify"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    headers = {"Authorization": "Bearer " + token}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    data = {"message": message}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    requests.post(url, headers=headers, data=data)</t>
+  </si>
+  <si>
+    <t># 在報告存檔成功後呼叫此函數</t>
+  </si>
+  <si>
+    <t>send_line_notify("📢 今日籌碼報告已更新！\n" + report_content, "你的Token")</t>
+  </si>
+  <si>
+    <t>第三階段：N100 伺服器排程 (Crontab)</t>
+  </si>
+  <si>
+    <t>當手動測試發送成功後，我們就會在 N100 設定 Crontab。這樣每天下午三點（或是資料收盤完整後的時間），N100 就會自動：</t>
+  </si>
+  <si>
+    <t>啟動 venv-linux。</t>
+  </si>
+  <si>
+    <t>執行 爬蟲抓資料。</t>
+  </si>
+  <si>
+    <t>發送 LINE 通知到你手機。</t>
+  </si>
+  <si>
+    <t>同步 回 GitHub 備份。</t>
+  </si>
+  <si>
+    <t>3. 為什麼要設定這個？</t>
+  </si>
+  <si>
+    <t>即時性：資料一出來（約下午 2:30 ~ 3:00），手機馬上震動，不用手動打開電腦看報告。</t>
+  </si>
+  <si>
+    <t>視覺化：除了文字，我們甚至可以讓它把當天的多空指標整理成簡單的圖示（例如：🔴 外資偏多 / 🟢 外資偏空）。</t>
+  </si>
+  <si>
+    <t>免費穩定：LINE Notify 是完全免費的，且發送速度極快。</t>
+  </si>
+  <si>
+    <t>如果你感興趣，我們可以先從「取得 LINE Token」開始，我再幫你把發送功能寫進你的 daytime_query.py 裡，你想試試看嗎？</t>
+  </si>
+  <si>
+    <t>Taifex_LINE_Setup_Log.txt</t>
+  </si>
+  <si>
+    <t>LINE Messaging API 多人群組通知設定紀錄</t>
+  </si>
+  <si>
+    <t>一、 環境資訊</t>
+  </si>
+  <si>
+    <r>
+      <t>專案路徑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>C:\AI\Taifex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Python 虛擬環境</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>venv-win</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>必要套件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (已於 2026/01/17 安裝完成)</t>
+    </r>
+  </si>
+  <si>
+    <t>二、 LINE 開發者設定紀錄</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Provider (提供者)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DM.Nice</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Channel 名稱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DM - AI通知助手</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Messaging API 設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Webhook URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://webhook.site/42fd03a6-6fd2-4feb-8017-c58f21fef494</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>加入群組功能 (Allow bot to join group chats)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：已開啟 (Enabled)</t>
+    </r>
+  </si>
+  <si>
+    <t>三、 金鑰與 ID 資訊</t>
+  </si>
+  <si>
+    <r>
+      <t>Channel Access Token</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">： </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>YyFz6dpvNqqHc0M5gEEY4iJMgRVlYQY8YsF7nRRsuiTeMdImY4M64UyLtYBQBh26TEb9KC/gCaQDj0HLVXcX3SfqrW+kUYVEvoDTcATUXtboiacQ8II2TmfaT5AfpHRb+PA9hK32lRpBX+5im7kdkQdB04t89/1O/w1cDnyilFU=</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>測試群組 ID (groupId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">： </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>C06180c9e6ef756d8c4ef6da0f2bc277c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>四、 最終運作程式碼 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>line.py</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">用法  :   python line_msg.py </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="20"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>send_data.txt</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F17: 打開 網址 https://www.twse.com.tw/fund/BFI82U                              台灣股票外資及陸資    [請填入:買賣差額]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F16: 打開 網址 https://www.twse.com.tw/zh/trading/historical/stock-day.html     2330 台積電-當日(1000股=1張)  [請填入:成交張數]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F15: 打開 網址 https://www.twse.com.tw/zh/trading/historical/stock-day.html     2330 台積電-當日    [請填入:漲跌價差]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F14: 打開 網址 https://www.twse.com.tw/zh/trading/historical/stock-day.html     2330 台積電-當日    [請填入:收盤價]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F12: 打開 網址 https://www.twse.com.tw/zh/trading/historical/mi-index.html      大盤統計資訊  [請填入:總計成交金額]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F11: 打開 網址 https://www.twse.com.tw/zh/indices/taiex/mi-5min-hist.html       加權股價     [請填入:指數收盤]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F07: 打開 網址 https://www.taifex.com.tw/cht/3/pcRatio                臺指選擇權Put/Call比  [請填入:買賣權未平倉量比率%]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F06: 打開 網址 https://mis.taifex.com.tw/futures/VolatilityQuotes     臺指選擇權波動率指數   [請填入:波動率指數]            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F05: 打開 網址 https://www.taifex.com.tw/cht/3/optDailyMarketReport   台指期貨-當日選擇權    [請填入:選擇權總成交量] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F04: 打開 網址 https://www.taifex.com.tw/cht/3/futDailyMarketReport   台指期貨-當日收盤價    [請填入:最後成交價] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F03: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   台指期貨-外資 [請填入:未平倉 空方口數] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F02: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   台指期貨-外資 [請填入:未平倉 多方口數] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            F01: 打開 網址 https://www.taifex.com.tw/cht/3/totalTableDate   台指期貨-外資 [請填入:未平倉 多空淨額口數] </t>
-  </si>
-  <si>
-    <t>一般交易時段</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 查當日資料 當日無資料 轉查前一個交易日資料</t>
-  </si>
-  <si>
-    <t>💡 一個讓 Ubuntu 使用更順暢的小建議</t>
-  </si>
-  <si>
-    <t>如果你之後發現 claude 還是常噴權限錯誤，最好的長期解法是把全域 npm 的目錄改到你的家目錄下，這樣以後裝任何工具都不需要 sudo：</t>
-  </si>
-  <si>
-    <t>Bash</t>
-  </si>
-  <si>
-    <t># 建立一個給全域使用的目錄</t>
-  </si>
-  <si>
-    <t>mkdir ~/.npm-global</t>
-  </si>
-  <si>
-    <t># 設定 npm 使用新路徑</t>
-  </si>
-  <si>
-    <t>npm config set prefix '~/.npm-global'</t>
-  </si>
-  <si>
-    <t># 把路徑加入你的 .bashrc</t>
-  </si>
-  <si>
-    <t>echo 'export PATH=~/.npm-global/bin:$PATH' &gt;&gt; ~/.bashrc</t>
-  </si>
-  <si>
-    <t>source ~/.bashrc</t>
-  </si>
-  <si>
-    <t># 之後安裝就不用 sudo 了：npm install -g @anthropic-ai/claude-code</t>
-  </si>
-  <si>
-    <t>現在請試著執行 claude，看看能不能順利看到對話視窗？</t>
+    <t>import os</t>
+  </si>
+  <si>
+    <t>import sys</t>
+  </si>
+  <si>
+    <t>from dotenv import load_dotenv</t>
+  </si>
+  <si>
+    <t># 從環境變數中取得資訊</t>
+  </si>
+  <si>
+    <t># 填入您剛領取的 2項 資訊</t>
+  </si>
+  <si>
+    <t># 載入 .env 檔案中的環境變數</t>
+  </si>
+  <si>
+    <t># TOKEN =  LINE 認證金鑰</t>
+  </si>
+  <si>
+    <t># GROUP_ID =  目標群組 ID</t>
+  </si>
+  <si>
+    <t>load_dotenv()</t>
+  </si>
+  <si>
+    <t>TOKEN = os.getenv("LINE_CHANNEL_ACCESS_TOKEN")</t>
+  </si>
+  <si>
+    <t>GROUP_ID = os.getenv("LINE_GROUP_ID")</t>
+  </si>
+  <si>
+    <t>def send_to_group(message):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """發送訊息至 LINE 群組"""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not TOKEN or not GROUP_ID:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print("錯誤：找不到環境變數，請檢查 .env 檔案設定")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    url = "https://api.line.me/v2/bot/message/push"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    headers = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "Content-Type": "application/json",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "Authorization": f"Bearer {TOKEN}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    payload = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "to": GROUP_ID,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "messages": [{"type": "text", "text": message}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    res = requests.post(url, headers=headers, json=payload)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if res.status_code == 200:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print("成功發送至 LINE 群組")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(f"錯誤碼：{res.status_code}, 內容：{res.text}")</t>
+  </si>
+  <si>
+    <t>def read_file_content(file_path):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    """讀取檔案內容"""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if not os.path.exists(file_path):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(f"錯誤：檔案不存在 - {file_path}")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    with open(file_path, "r", encoding="utf-8") as f:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return f.read()</t>
+  </si>
+  <si>
+    <t>if __name__ == "__main__":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if len(sys.argv) &lt; 2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print("使用方式: python line_msg.py &lt;檔案路徑&gt;")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print("範例: python line_msg.py C:\\AI\\Taifex\\output\\taifex_night_2026.01.20_v4.md")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        sys.exit(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    file_path = sys.argv[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    content = read_file_content(file_path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if content:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        send_to_group(content)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -941,6 +1568,73 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="20"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -980,7 +1674,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1021,6 +1715,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,6 +2004,50 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7076190" cy="9885714"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="圖片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A5EE524-4314-47C3-B512-B69004D3B5D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14439900" y="323850"/>
+          <a:ext cx="7076190" cy="9885714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1653,22 +2433,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>11010900</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7390476" cy="6123809"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>14582329</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>275504</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="圖片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0B79509-BCF0-439D-BCCB-D359C114129B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{939C0A97-BCD3-44F3-868B-B512B20BFE9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1684,8 +2469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2057400" y="4562475"/>
-          <a:ext cx="7390476" cy="6123809"/>
+          <a:off x="12382500" y="24422100"/>
+          <a:ext cx="3571429" cy="5771429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1693,21 +2478,26 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2162175</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7076190" cy="9885714"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>6990746</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>37730</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="圖片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A5EE524-4314-47C3-B512-B69004D3B5D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AEFEB27-A9EA-45B5-9F89-4CF3BF8FCC72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1723,8 +2513,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2571750" y="3829050"/>
-          <a:ext cx="7076190" cy="9885714"/>
+          <a:off x="3533775" y="32880300"/>
+          <a:ext cx="4828571" cy="2961905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1732,85 +2522,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="14485714" cy="7085714"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="圖片 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD434205-C1CC-43D4-9978-21FD5F92A00C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="714375" y="10991850"/>
-          <a:ext cx="14485714" cy="7085714"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="12504762" cy="8457143"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="圖片 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C61DA83-12C1-4B67-9462-BAF5268F19DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1409700" y="20364450"/>
-          <a:ext cx="12504762" cy="8457143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2235,6 +2947,301 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4C375C-2ECA-4A97-8860-CF69A550CA8F}">
+  <dimension ref="C1:C60"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="143.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:3">
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3">
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3">
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3">
+      <c r="C46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3">
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3">
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3">
+      <c r="C55" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3">
+      <c r="C56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3">
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11A6911-FE15-40E5-A844-54591F1F9FA6}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -2438,117 +3445,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4C375C-2ECA-4A97-8860-CF69A550CA8F}">
-  <dimension ref="C3:C95"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="3" max="3" width="143.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3">
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3">
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3">
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3">
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3">
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="3:3">
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3">
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="3:3">
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="3:3">
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" s="3" customFormat="1"/>
-    <row r="95" spans="3:3">
-      <c r="C95" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511DB973-6FBF-4E18-AD22-36135CFC2472}">
   <dimension ref="C4:C21"/>
@@ -2560,64 +3456,64 @@
     <row r="4" spans="3:3" s="2" customFormat="1" ht="27.75"/>
     <row r="5" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="3:3" s="2" customFormat="1" ht="27.75"/>
     <row r="8" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="3:3" s="2" customFormat="1" ht="27.75"/>
     <row r="10" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C10" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C15" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="3:3" s="2" customFormat="1" ht="27.75">
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="3:3" s="2" customFormat="1" ht="27.75"/>
@@ -2627,4 +3523,709 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A07E2DF-578D-49C5-9BA6-7E4D54350D27}">
+  <dimension ref="C4:C73"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="199" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:3" ht="21">
+      <c r="C4" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="21">
+      <c r="C5" s="14"/>
+    </row>
+    <row r="6" spans="3:3" ht="21">
+      <c r="C6" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="21">
+      <c r="C7" s="14"/>
+    </row>
+    <row r="8" spans="3:3" ht="21">
+      <c r="C8" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="21">
+      <c r="C9" s="14"/>
+    </row>
+    <row r="10" spans="3:3" ht="21">
+      <c r="C10" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="21">
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="3:3" ht="21">
+      <c r="C12" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="21">
+      <c r="C13" s="14"/>
+    </row>
+    <row r="14" spans="3:3" ht="21">
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="3:3" ht="21">
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="3:3" ht="21">
+      <c r="C16" s="14"/>
+    </row>
+    <row r="17" spans="3:3" ht="21">
+      <c r="C17" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="21">
+      <c r="C18" s="14"/>
+    </row>
+    <row r="19" spans="3:3" ht="21">
+      <c r="C19" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="21">
+      <c r="C20" s="14"/>
+    </row>
+    <row r="21" spans="3:3" ht="21">
+      <c r="C21" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" ht="21">
+      <c r="C22" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" ht="21">
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="3:3" ht="21">
+      <c r="C24" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" ht="21">
+      <c r="C25" s="14"/>
+    </row>
+    <row r="26" spans="3:3" ht="21">
+      <c r="C26" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" ht="21">
+      <c r="C27" s="14"/>
+    </row>
+    <row r="28" spans="3:3" ht="21">
+      <c r="C28" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" ht="21">
+      <c r="C29" s="14"/>
+    </row>
+    <row r="30" spans="3:3" ht="21">
+      <c r="C30" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" ht="21">
+      <c r="C31" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3" ht="21">
+      <c r="C32" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" ht="21">
+      <c r="C33" s="14"/>
+    </row>
+    <row r="34" spans="3:3" ht="21">
+      <c r="C34" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" ht="21">
+      <c r="C35" s="14"/>
+    </row>
+    <row r="36" spans="3:3" ht="21">
+      <c r="C36" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" ht="21">
+      <c r="C37" s="14"/>
+    </row>
+    <row r="38" spans="3:3" ht="21">
+      <c r="C38" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" ht="21">
+      <c r="C39" s="14"/>
+    </row>
+    <row r="40" spans="3:3" ht="21">
+      <c r="C40" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" ht="21">
+      <c r="C41" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" ht="21">
+      <c r="C42" s="14"/>
+    </row>
+    <row r="43" spans="3:3" ht="21">
+      <c r="C43" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" ht="21">
+      <c r="C44" s="14"/>
+    </row>
+    <row r="45" spans="3:3" ht="21">
+      <c r="C45" s="14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" ht="21">
+      <c r="C46" s="14"/>
+    </row>
+    <row r="47" spans="3:3" ht="21">
+      <c r="C47" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" ht="21">
+      <c r="C48" s="14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" ht="21">
+      <c r="C49" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" ht="21">
+      <c r="C50" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" ht="21">
+      <c r="C51" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" ht="21">
+      <c r="C52" s="14"/>
+    </row>
+    <row r="53" spans="3:3" ht="21">
+      <c r="C53" s="14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" ht="21">
+      <c r="C54" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" ht="21">
+      <c r="C55" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" ht="21">
+      <c r="C56" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" ht="21">
+      <c r="C57" s="14"/>
+    </row>
+    <row r="58" spans="3:3" ht="21">
+      <c r="C58" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" ht="21">
+      <c r="C59" s="14"/>
+    </row>
+    <row r="60" spans="3:3" ht="21">
+      <c r="C60" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" ht="21">
+      <c r="C61" s="14"/>
+    </row>
+    <row r="62" spans="3:3" ht="21">
+      <c r="C62" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" ht="21">
+      <c r="C63" s="14"/>
+    </row>
+    <row r="64" spans="3:3" ht="21">
+      <c r="C64" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" ht="21">
+      <c r="C65" s="14"/>
+    </row>
+    <row r="66" spans="3:3" ht="21">
+      <c r="C66" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" ht="21">
+      <c r="C67" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" ht="21">
+      <c r="C68" s="14"/>
+    </row>
+    <row r="69" spans="3:3" ht="21">
+      <c r="C69" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" ht="21">
+      <c r="C70" s="14"/>
+    </row>
+    <row r="71" spans="3:3" ht="21">
+      <c r="C71" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" ht="21">
+      <c r="C72" s="14"/>
+    </row>
+    <row r="73" spans="3:3" ht="21">
+      <c r="C73" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3395A2-CCF6-4B9E-B00F-FCF6FB3D3EA5}">
+  <dimension ref="C3:C115"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="197.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" s="15" customFormat="1" ht="36.75">
+      <c r="C3" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" ht="27.75">
+      <c r="C6" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="27.75">
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8" spans="3:3" ht="27.75">
+      <c r="C8" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="27.75">
+      <c r="C9" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" ht="27.75">
+      <c r="C10" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="27.75">
+      <c r="C11" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" ht="27.75">
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="3:3" ht="27.75">
+      <c r="C13" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="27.75">
+      <c r="C14" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" ht="27.75">
+      <c r="C15" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" ht="27.75">
+      <c r="C16" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" ht="27.75">
+      <c r="C17" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="27.75">
+      <c r="C18" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="27.75">
+      <c r="C19" s="19"/>
+    </row>
+    <row r="20" spans="3:3" ht="27.75">
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" spans="3:3" ht="27.75">
+      <c r="C21" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" ht="27.75">
+      <c r="C22" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" ht="27.75">
+      <c r="C23" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" s="3" customFormat="1" ht="27.75">
+      <c r="C25" s="20"/>
+    </row>
+    <row r="27" spans="3:3" ht="27.75">
+      <c r="C27" s="18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" ht="27.75">
+      <c r="C28" s="18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" s="8" customFormat="1" ht="27.75">
+      <c r="C29" s="19"/>
+    </row>
+    <row r="30" spans="3:3" ht="27.75">
+      <c r="C30" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" ht="27.75">
+      <c r="C31" s="17"/>
+    </row>
+    <row r="32" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C32" s="22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C33" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C34" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C35" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C36" s="22"/>
+    </row>
+    <row r="37" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C37" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C38" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C39" s="24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C40" s="22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C41" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C42" s="22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C43" s="22"/>
+    </row>
+    <row r="44" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C44" s="22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C45" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C46" s="22"/>
+    </row>
+    <row r="47" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C47" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C48" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C49" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C50" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C51" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C52" s="22"/>
+    </row>
+    <row r="53" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C53" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C54" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C55" s="25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C56" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" s="26" customFormat="1" ht="27.75">
+      <c r="C57" s="26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C58" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C59" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C60" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C61" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C62" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="64" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C64" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C65" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C66" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C67" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C68" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C69" s="23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="71" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C71" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C72" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C73" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C74" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C75" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="77" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C77" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C78" s="23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="80" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C80" s="23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C81" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C82" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C83" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C84" s="23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="86" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C86" s="23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C87" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" s="23" customFormat="1" ht="27.75"/>
+    <row r="89" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C89" s="23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C90" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" s="23" customFormat="1" ht="27.75">
+      <c r="C91" s="23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" s="27" customFormat="1" ht="27.75"/>
+    <row r="95" spans="3:3" ht="27.75">
+      <c r="C95" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" s="3" customFormat="1"/>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>